--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_aysen.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:11</t>
+    <t xml:space="preserve">2026-09-24 01:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -774,13 +774,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>-0.13</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         <v>0.3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0.24</v>
@@ -1119,13 +1119,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>-0.13</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="27">
@@ -1421,10 +1421,10 @@
         <v>0.08</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="40">
@@ -1470,7 +1470,7 @@
         <v>0.11</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="42">
@@ -1513,10 +1513,10 @@
         <v>0.09</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="44">
@@ -1536,10 +1536,10 @@
         <v>-0.11</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.29</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="45">
@@ -1809,13 +1809,13 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="57">
@@ -1881,10 +1881,10 @@
         <v>-0.69</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="60">
@@ -2157,7 +2157,7 @@
         <v>0.32</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>0.06</v>
@@ -2433,10 +2433,10 @@
         <v>-0.07</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2456,10 +2456,10 @@
         <v>-0.48</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="85">
@@ -2482,7 +2482,7 @@
         <v>-0.06</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="86">
@@ -2499,13 +2499,13 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="87">
@@ -2778,10 +2778,10 @@
         <v>0.19</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="99">
@@ -2804,7 +2804,7 @@
         <v>-0.42</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="100">
@@ -2827,7 +2827,7 @@
         <v>0.01</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="101">
@@ -2893,10 +2893,10 @@
         <v>0.15</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="104">
@@ -2916,10 +2916,10 @@
         <v>-0.04</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="105">
@@ -3123,7 +3123,7 @@
         <v>0.26</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>0.55</v>
@@ -3146,10 +3146,10 @@
         <v>-0.23</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="115">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_aysen.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:01</t>
+    <t xml:space="preserve">2026-10-01 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_aysen.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:09</t>
+    <t xml:space="preserve">2026-10-05 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
